--- a/BOM/EXCEL/MAIN TEMPLATE.xlsx
+++ b/BOM/EXCEL/MAIN TEMPLATE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DANIEL\ANTIGRAVITY\PROJEK\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DANIEL\ANTIGRAVITY\PROJEK\BOM\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931CAC51-EAC7-406B-BEAA-414C62405772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A80DF8C-2970-4308-BA9D-6013F17D3361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t>Material</t>
   </si>
@@ -417,90 +417,12 @@
   <si>
     <t>Indicator: Multiple Specifications</t>
   </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>NORM</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>MWST</t>
-  </si>
-  <si>
-    <t>0001</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>PD</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>KP</t>
-  </si>
-  <si>
-    <t>ZMG1</t>
-  </si>
-  <si>
-    <t>HALB</t>
-  </si>
-  <si>
-    <t>HSF004</t>
-  </si>
-  <si>
-    <t>PC</t>
-  </si>
-  <si>
-    <t>M3</t>
-  </si>
-  <si>
-    <t>33X37X190</t>
-  </si>
-  <si>
-    <t>SF01</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>KG</t>
-  </si>
-  <si>
-    <t>GT1</t>
-  </si>
-  <si>
-    <t>EX</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>Ini testing Tab pada Material</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>ZWH6</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="15">
+  <numFmts count="13">
     <numFmt numFmtId="5" formatCode="&quot;Rp&quot;#,##0;\-&quot;Rp&quot;#,##0"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
@@ -514,10 +436,8 @@
     <numFmt numFmtId="170" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
     <numFmt numFmtId="171" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="172" formatCode="&quot;Rp&quot;#.##0_);\(&quot;Rp&quot;#.##0\)"/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="77">
+  <fonts count="75">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -563,12 +483,6 @@
       <sz val="10"/>
       <name val="MS Sans Serif"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1054,19 +968,13 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="57">
+  <fills count="56">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1362,14 +1270,8 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="28">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1688,34 +1590,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="7311">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1727,242 +1601,242 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="50" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="51" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="52" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="53" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="54" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="55" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="57" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="49" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="50" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="51" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="52" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="53" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="54" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="56" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1975,301 +1849,301 @@
     <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="39" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="41" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="62" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="40" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="36" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="38" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2291,7 +2165,7 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -2320,7 +2194,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
@@ -2332,7 +2206,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
@@ -2353,18 +2227,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
@@ -2389,51 +2263,51 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -2445,24 +2319,24 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2470,11 +2344,11 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2482,154 +2356,154 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -2643,52 +2517,52 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="50" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="51" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="52" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="53" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="54" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="55" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="57" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="49" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="50" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="51" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="52" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="53" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="54" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="56" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2703,77 +2577,77 @@
     <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="39" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="41" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="62" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="40" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="36" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="38" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="57" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="56" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="54" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="55" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="53" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="54" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="53" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="51" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="52" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="50" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="52" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="51" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="61" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2788,56 +2662,56 @@
     <xf numFmtId="0" fontId="2" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="61" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="61" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="50" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="39" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="41" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="49" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="40" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2857,133 +2731,425 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="62" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
@@ -3007,7 +3173,92 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
@@ -3027,447 +3278,70 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="38" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3509,876 +3383,876 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="72" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="71" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="72" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="71" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="72" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="71" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="72" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="71" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="72" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="71" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="72" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="71" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="72" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="71" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="72" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="71" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="5" fontId="68" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="5" fontId="67" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -4394,11 +4268,11 @@
     <xf numFmtId="0" fontId="2" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="62" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="5" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -4410,7 +4284,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="36" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -4441,23 +4315,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -4467,35 +4341,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="38" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
@@ -4505,32 +4379,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="62" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -4540,261 +4414,261 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="5" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="29" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="5" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="5" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="5" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
@@ -4802,10 +4676,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -4813,7 +4687,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -4823,28 +4697,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="62" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="40" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -4852,43 +4726,43 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="5" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -4903,27 +4777,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="62" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="40" fillId="30" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -4931,62 +4805,62 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="45" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -6004,7 +5878,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -6040,14 +5914,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -6060,7 +5934,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -6779,9 +6653,9 @@
     <xf numFmtId="0" fontId="4" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -8973,154 +8847,133 @@
     <xf numFmtId="0" fontId="4" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="56" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="56" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="56" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="56" borderId="27" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="56" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="56" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7311">
@@ -16734,7 +16587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:EI2"/>
+  <dimension ref="A1:ED1"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -16855,7 +16708,7 @@
     <col min="134" max="134" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:139" ht="28" customHeight="1">
+    <row r="1" spans="1:134" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -17255,285 +17108,6 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:139" s="4" customFormat="1" ht="15.5">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3">
-        <v>0</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="N2" s="3">
-        <v>2000</v>
-      </c>
-      <c r="O2" s="3">
-        <v>2233</v>
-      </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="U2" s="3">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE2" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="AF2" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG2" s="3"/>
-      <c r="AH2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="AI2" s="3">
-        <v>200301</v>
-      </c>
-      <c r="AJ2" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="AK2" s="3">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="AL2" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM2" s="3">
-        <v>1</v>
-      </c>
-      <c r="AN2" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="AO2" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP2" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ2" s="3"/>
-      <c r="AR2" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS2" s="3"/>
-      <c r="AT2" s="3"/>
-      <c r="AU2" s="3"/>
-      <c r="AV2" s="3"/>
-      <c r="AW2" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX2" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="AY2" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ2" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA2" s="3"/>
-      <c r="BB2" s="3"/>
-      <c r="BC2" s="3"/>
-      <c r="BD2" s="3"/>
-      <c r="BE2" s="3"/>
-      <c r="BF2" s="3"/>
-      <c r="BG2" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="BH2" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="BI2" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="BJ2" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="BK2" s="3"/>
-      <c r="BL2" s="3"/>
-      <c r="BM2" s="3"/>
-      <c r="BN2" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="BO2" s="3"/>
-      <c r="BP2" s="3">
-        <v>1</v>
-      </c>
-      <c r="BQ2" s="3">
-        <v>0</v>
-      </c>
-      <c r="BR2" s="3"/>
-      <c r="BS2" s="3">
-        <v>0</v>
-      </c>
-      <c r="BT2" s="3">
-        <v>0</v>
-      </c>
-      <c r="BU2" s="3"/>
-      <c r="BV2" s="3">
-        <v>20</v>
-      </c>
-      <c r="BW2" s="3"/>
-      <c r="BX2" s="3"/>
-      <c r="BY2" s="3"/>
-      <c r="BZ2" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="CA2" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="CB2" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="CC2" s="3"/>
-      <c r="CD2" s="3">
-        <v>1</v>
-      </c>
-      <c r="CE2" s="3"/>
-      <c r="CF2" s="3"/>
-      <c r="CG2" s="3">
-        <v>1207</v>
-      </c>
-      <c r="CH2" s="6"/>
-      <c r="CI2" s="3">
-        <v>0</v>
-      </c>
-      <c r="CJ2" s="3">
-        <v>0</v>
-      </c>
-      <c r="CK2" s="3"/>
-      <c r="CL2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="CM2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="CN2" s="3">
-        <v>100</v>
-      </c>
-      <c r="CO2" s="3"/>
-      <c r="CP2" s="5"/>
-      <c r="CQ2" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="CR2" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="CS2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="CT2" s="3"/>
-      <c r="CU2" s="3"/>
-      <c r="CV2" s="3"/>
-      <c r="CW2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="CX2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="CY2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="CZ2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="DA2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="DB2" s="3"/>
-      <c r="DC2" s="3">
-        <v>0</v>
-      </c>
-      <c r="DD2" s="3"/>
-      <c r="DE2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="DF2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="DG2" s="3"/>
-      <c r="DH2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="DI2" s="3">
-        <v>0</v>
-      </c>
-      <c r="DJ2" s="3"/>
-      <c r="DK2" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="DL2" s="3">
-        <v>6</v>
-      </c>
-      <c r="DM2" s="3"/>
-      <c r="DN2" s="3"/>
-      <c r="DO2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="DP2" s="3"/>
-      <c r="DQ2" s="3"/>
-      <c r="DR2" s="3"/>
-      <c r="DS2" s="3"/>
-      <c r="DT2" s="3"/>
-      <c r="DU2" s="3"/>
-      <c r="DV2" s="3"/>
-      <c r="DW2" s="3"/>
-      <c r="DX2" s="3"/>
-      <c r="DY2" s="3"/>
-      <c r="DZ2" s="3"/>
-      <c r="EA2" s="3"/>
-      <c r="EB2" s="3"/>
-      <c r="EC2" s="3"/>
-      <c r="ED2" s="3"/>
-      <c r="EE2" s="2"/>
-      <c r="EF2" s="3"/>
-      <c r="EG2" s="3"/>
-      <c r="EH2" s="3"/>
-      <c r="EI2" s="3"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
